--- a/data/example/data_formatting/obs_columns_matching_examples/sex_matching_table.xlsx
+++ b/data/example/data_formatting/obs_columns_matching_examples/sex_matching_table.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,6 +473,21 @@
       </c>
       <c r="C3" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
